--- a/artfynd/A 52392-2025 artfynd.xlsx
+++ b/artfynd/A 52392-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
         <v>131143907</v>
       </c>
       <c r="B5" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131143921</v>
       </c>
       <c r="B6" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>131143906</v>
       </c>
       <c r="B7" t="n">
-        <v>91810</v>
+        <v>91813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>131143942</v>
       </c>
       <c r="B8" t="n">
-        <v>92464</v>
+        <v>92467</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52392-2025 artfynd.xlsx
+++ b/artfynd/A 52392-2025 artfynd.xlsx
@@ -805,7 +805,7 @@
         <v>131143927</v>
       </c>
       <c r="B3" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131143928</v>
       </c>
       <c r="B4" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131143907</v>
       </c>
       <c r="B5" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131143921</v>
       </c>
       <c r="B6" t="n">
-        <v>92111</v>
+        <v>92112</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>131143906</v>
       </c>
       <c r="B7" t="n">
-        <v>91813</v>
+        <v>91814</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>131143942</v>
       </c>
       <c r="B8" t="n">
-        <v>92467</v>
+        <v>92468</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52392-2025 artfynd.xlsx
+++ b/artfynd/A 52392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143911</v>
       </c>
       <c r="B2" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>131143927</v>
       </c>
       <c r="B3" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131143928</v>
       </c>
       <c r="B4" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131143907</v>
       </c>
       <c r="B5" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131143921</v>
       </c>
       <c r="B6" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>131143906</v>
       </c>
       <c r="B7" t="n">
-        <v>91814</v>
+        <v>91816</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>131143942</v>
       </c>
       <c r="B8" t="n">
-        <v>92468</v>
+        <v>92470</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52392-2025 artfynd.xlsx
+++ b/artfynd/A 52392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143911</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>131143927</v>
       </c>
       <c r="B3" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131143928</v>
       </c>
       <c r="B4" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131143907</v>
       </c>
       <c r="B5" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131143921</v>
       </c>
       <c r="B6" t="n">
-        <v>92114</v>
+        <v>92115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>131143906</v>
       </c>
       <c r="B7" t="n">
-        <v>91816</v>
+        <v>91817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>131143942</v>
       </c>
       <c r="B8" t="n">
-        <v>92470</v>
+        <v>92471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52392-2025 artfynd.xlsx
+++ b/artfynd/A 52392-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131143911</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>131143927</v>
       </c>
       <c r="B3" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>131143928</v>
       </c>
       <c r="B4" t="n">
-        <v>79254</v>
+        <v>79260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -999,7 +999,7 @@
         <v>131143907</v>
       </c>
       <c r="B5" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         <v>131143921</v>
       </c>
       <c r="B6" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>131143906</v>
       </c>
       <c r="B7" t="n">
-        <v>91822</v>
+        <v>91828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
         <v>131143942</v>
       </c>
       <c r="B8" t="n">
-        <v>92476</v>
+        <v>92482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 52392-2025 artfynd.xlsx
+++ b/artfynd/A 52392-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143920</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143921</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143922</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143906</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143907</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143908</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143942</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143925</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143926</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143927</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143928</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143929</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143930</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143918</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2165,6 +2240,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143911</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131143915</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2403,8 +2488,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127273036</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>